--- a/public/student_import_template.xlsx
+++ b/public/student_import_template.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="12330"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="الطلاب" state="visible" r:id="rId4"/>
+    <sheet name="الطلاب" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
   <si>
     <t>الاسم الأول</t>
   </si>
@@ -46,53 +49,25 @@
     <t>كلمة السرّ</t>
   </si>
   <si>
-    <t>يحيى</t>
-  </si>
-  <si>
-    <t>الحمود</t>
-  </si>
-  <si>
-    <t>محمد</t>
-  </si>
-  <si>
-    <t>رهف</t>
-  </si>
-  <si>
-    <t>ذكر</t>
-  </si>
-  <si>
     <t/>
-  </si>
-  <si>
-    <t>عهد</t>
-  </si>
-  <si>
-    <t>عبد الرحمن</t>
-  </si>
-  <si>
-    <t>محمود</t>
-  </si>
-  <si>
-    <t>ربيعة</t>
-  </si>
-  <si>
-    <t>أنثى</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -458,7 +433,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="11" width="16" customWidth="1"/>
   </cols>
@@ -499,77 +474,47 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>